--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,370 +394,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5428</v>
+        <v>4781</v>
       </c>
       <c r="B2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5388</v>
+        <v>4681</v>
       </c>
       <c r="B3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5284</v>
+        <v>4650</v>
       </c>
       <c r="B4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5287</v>
+        <v>4592</v>
       </c>
       <c r="B5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5213</v>
+        <v>4580</v>
       </c>
       <c r="B6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5274</v>
+        <v>4617</v>
       </c>
       <c r="B7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5284</v>
+        <v>4539</v>
       </c>
       <c r="B8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5249</v>
+        <v>4567</v>
       </c>
       <c r="B9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5376</v>
+        <v>4447</v>
       </c>
       <c r="B10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5356</v>
+        <v>4422</v>
       </c>
       <c r="B11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5344</v>
+        <v>4402</v>
       </c>
       <c r="B12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5352</v>
+        <v>4398</v>
       </c>
       <c r="B13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5400</v>
+        <v>4368</v>
       </c>
       <c r="B14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5421</v>
+        <v>4395</v>
       </c>
       <c r="B15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5383</v>
+        <v>4413</v>
       </c>
       <c r="B16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5396</v>
+        <v>4450</v>
       </c>
       <c r="B17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5418</v>
+        <v>4504</v>
       </c>
       <c r="B18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5408</v>
+        <v>4558</v>
       </c>
       <c r="B19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5384</v>
+        <v>4541</v>
       </c>
       <c r="B20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5415</v>
+        <v>4574</v>
       </c>
       <c r="B21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5613</v>
+        <v>4563</v>
       </c>
       <c r="B22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5633</v>
+        <v>4594</v>
       </c>
       <c r="B23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5634</v>
+        <v>4635</v>
       </c>
       <c r="B24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5698</v>
+        <v>4653</v>
       </c>
       <c r="B25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5880</v>
+        <v>4699</v>
       </c>
       <c r="B26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5954</v>
+        <v>4671</v>
       </c>
       <c r="B27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6024</v>
+        <v>4750</v>
       </c>
       <c r="B28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6067</v>
+        <v>4759</v>
       </c>
       <c r="B29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6057</v>
+        <v>4809</v>
       </c>
       <c r="B30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6051</v>
+        <v>4789</v>
       </c>
       <c r="B31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6032</v>
+        <v>4688</v>
       </c>
       <c r="B32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6008</v>
+        <v>4721</v>
       </c>
       <c r="B33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5780</v>
+        <v>4692</v>
       </c>
       <c r="B34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5781</v>
+        <v>4631</v>
       </c>
       <c r="B35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5648</v>
+        <v>4568</v>
       </c>
       <c r="B36" s="2">
-        <v>46269.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>5443</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46269.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>5280</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46269.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>5062</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46269.38541666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>4932</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46269.39583333334</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>4837</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46269.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>4736</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46269.41666666666</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>4789</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46269.42708333334</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>4791</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46269.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>4642</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46269.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>4752</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46269.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>4652</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46269.46875</v>
+        <v>46278.35416666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,282 +394,290 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4781</v>
+        <v>5025</v>
       </c>
       <c r="B2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4681</v>
+        <v>5000</v>
       </c>
       <c r="B3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4650</v>
+        <v>4953</v>
       </c>
       <c r="B4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4592</v>
+        <v>4926</v>
       </c>
       <c r="B5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4580</v>
+        <v>4875</v>
       </c>
       <c r="B6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4617</v>
+        <v>4833</v>
       </c>
       <c r="B7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4539</v>
+        <v>4846</v>
       </c>
       <c r="B8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4567</v>
+        <v>4807</v>
       </c>
       <c r="B9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4447</v>
+        <v>4814</v>
       </c>
       <c r="B10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4422</v>
+        <v>4882</v>
       </c>
       <c r="B11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4402</v>
+        <v>4895</v>
       </c>
       <c r="B12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4398</v>
+        <v>4879</v>
       </c>
       <c r="B13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4368</v>
+        <v>4900</v>
       </c>
       <c r="B14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4395</v>
+        <v>4922</v>
       </c>
       <c r="B15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4413</v>
+        <v>4946</v>
       </c>
       <c r="B16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4450</v>
+        <v>4969</v>
       </c>
       <c r="B17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4504</v>
+        <v>5106</v>
       </c>
       <c r="B18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4558</v>
+        <v>5132</v>
       </c>
       <c r="B19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4541</v>
+        <v>5091</v>
       </c>
       <c r="B20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4574</v>
+        <v>5117</v>
       </c>
       <c r="B21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4563</v>
+        <v>5299</v>
       </c>
       <c r="B22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>4594</v>
+        <v>5404</v>
       </c>
       <c r="B23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>4635</v>
+        <v>5532</v>
       </c>
       <c r="B24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>4653</v>
+        <v>5601</v>
       </c>
       <c r="B25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>4699</v>
+        <v>5811</v>
       </c>
       <c r="B26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>4671</v>
+        <v>5936</v>
       </c>
       <c r="B27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>4750</v>
+        <v>5954</v>
       </c>
       <c r="B28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>4759</v>
+        <v>5872</v>
       </c>
       <c r="B29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>4809</v>
+        <v>5978</v>
       </c>
       <c r="B30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>4789</v>
+        <v>6008</v>
       </c>
       <c r="B31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>4688</v>
+        <v>5646</v>
       </c>
       <c r="B32" s="2">
-        <v>46278.3125</v>
+        <v>46283.35416666666</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>4721</v>
+        <v>5719</v>
       </c>
       <c r="B33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.36458333334</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>4692</v>
+        <v>5387</v>
       </c>
       <c r="B34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>4631</v>
+        <v>5299</v>
       </c>
       <c r="B35" s="2">
-        <v>46278.34375</v>
+        <v>46283.38541666666</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>4568</v>
+        <v>5211</v>
       </c>
       <c r="B36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.39583333334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>5092</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46283.40625</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,290 +394,306 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5025</v>
+        <v>4610</v>
       </c>
       <c r="B2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5000</v>
+        <v>4614</v>
       </c>
       <c r="B3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4953</v>
+        <v>4640</v>
       </c>
       <c r="B4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4926</v>
+        <v>4588</v>
       </c>
       <c r="B5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4875</v>
+        <v>4648</v>
       </c>
       <c r="B6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4833</v>
+        <v>4583</v>
       </c>
       <c r="B7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4846</v>
+        <v>4545</v>
       </c>
       <c r="B8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4807</v>
+        <v>4529</v>
       </c>
       <c r="B9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4814</v>
+        <v>4402</v>
       </c>
       <c r="B10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4882</v>
+        <v>4399</v>
       </c>
       <c r="B11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4895</v>
+        <v>4357</v>
       </c>
       <c r="B12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4879</v>
+        <v>4352</v>
       </c>
       <c r="B13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4900</v>
+        <v>4354</v>
       </c>
       <c r="B14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4922</v>
+        <v>4365</v>
       </c>
       <c r="B15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4946</v>
+        <v>4353</v>
       </c>
       <c r="B16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4969</v>
+        <v>4401</v>
       </c>
       <c r="B17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5106</v>
+        <v>4377</v>
       </c>
       <c r="B18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5132</v>
+        <v>4354</v>
       </c>
       <c r="B19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5091</v>
+        <v>4377</v>
       </c>
       <c r="B20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5117</v>
+        <v>4391</v>
       </c>
       <c r="B21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5299</v>
+        <v>4440</v>
       </c>
       <c r="B22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5404</v>
+        <v>4458</v>
       </c>
       <c r="B23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5532</v>
+        <v>4449</v>
       </c>
       <c r="B24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5601</v>
+        <v>4412</v>
       </c>
       <c r="B25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5811</v>
+        <v>4417</v>
       </c>
       <c r="B26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>5936</v>
+        <v>4429</v>
       </c>
       <c r="B27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>5954</v>
+        <v>4420</v>
       </c>
       <c r="B28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>5872</v>
+        <v>4325</v>
       </c>
       <c r="B29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>5978</v>
+        <v>4302</v>
       </c>
       <c r="B30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6008</v>
+        <v>4305</v>
       </c>
       <c r="B31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>5646</v>
+        <v>4231</v>
       </c>
       <c r="B32" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>5719</v>
+        <v>4114</v>
       </c>
       <c r="B33" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>5387</v>
+        <v>4039</v>
       </c>
       <c r="B34" s="2">
-        <v>46283.375</v>
+        <v>46285.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>5299</v>
+        <v>3903</v>
       </c>
       <c r="B35" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>5211</v>
+        <v>3785</v>
       </c>
       <c r="B36" s="2">
-        <v>46283.39583333334</v>
+        <v>46285.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>5092</v>
+        <v>3649</v>
       </c>
       <c r="B37" s="2">
-        <v>46283.40625</v>
+        <v>46285.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>3540</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46285.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>3421</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46285.38541666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,306 +394,314 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4610</v>
+        <v>5019</v>
       </c>
       <c r="B2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4614</v>
+        <v>4994</v>
       </c>
       <c r="B3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4640</v>
+        <v>4979</v>
       </c>
       <c r="B4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4588</v>
+        <v>4931</v>
       </c>
       <c r="B5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4648</v>
+        <v>4987</v>
       </c>
       <c r="B6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4583</v>
+        <v>4907</v>
       </c>
       <c r="B7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4545</v>
+        <v>4944</v>
       </c>
       <c r="B8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4529</v>
+        <v>4940</v>
       </c>
       <c r="B9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4402</v>
+        <v>4967</v>
       </c>
       <c r="B10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4399</v>
+        <v>4934</v>
       </c>
       <c r="B11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4357</v>
+        <v>5145</v>
       </c>
       <c r="B12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4352</v>
+        <v>5103</v>
       </c>
       <c r="B13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4354</v>
+        <v>5062</v>
       </c>
       <c r="B14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4365</v>
+        <v>5040</v>
       </c>
       <c r="B15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4353</v>
+        <v>5127</v>
       </c>
       <c r="B16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4401</v>
+        <v>5242</v>
       </c>
       <c r="B17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4377</v>
+        <v>5201</v>
       </c>
       <c r="B18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4354</v>
+        <v>5228</v>
       </c>
       <c r="B19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4377</v>
+        <v>5350</v>
       </c>
       <c r="B20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4391</v>
+        <v>5433</v>
       </c>
       <c r="B21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>4440</v>
+        <v>5625</v>
       </c>
       <c r="B22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>4458</v>
+        <v>5618</v>
       </c>
       <c r="B23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>4449</v>
+        <v>5745</v>
       </c>
       <c r="B24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>4412</v>
+        <v>5917</v>
       </c>
       <c r="B25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>4417</v>
+        <v>6064</v>
       </c>
       <c r="B26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>4429</v>
+        <v>6231</v>
       </c>
       <c r="B27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>4420</v>
+        <v>6312</v>
       </c>
       <c r="B28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>4325</v>
+        <v>6300</v>
       </c>
       <c r="B29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>4302</v>
+        <v>6278</v>
       </c>
       <c r="B30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>4305</v>
+        <v>6324</v>
       </c>
       <c r="B31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>4231</v>
+        <v>6224</v>
       </c>
       <c r="B32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>4114</v>
+        <v>6112</v>
       </c>
       <c r="B33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>4039</v>
+        <v>5868</v>
       </c>
       <c r="B34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>3903</v>
+        <v>5770</v>
       </c>
       <c r="B35" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>3785</v>
+        <v>5641</v>
       </c>
       <c r="B36" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>3649</v>
+        <v>5505</v>
       </c>
       <c r="B37" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>3540</v>
+        <v>5199</v>
       </c>
       <c r="B38" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>3421</v>
+        <v>5088</v>
       </c>
       <c r="B39" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>5110</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46295.39583333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -26,9 +26,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -81,12 +78,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -392,318 +388,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>5019</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>4994</v>
-      </c>
-      <c r="B3" s="2">
-        <v>46295.01041666666</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>4979</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46295.02083333334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4931</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46295.03125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>4987</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46295.04166666666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>4907</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46295.05208333334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>4944</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46295.0625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>4940</v>
-      </c>
-      <c r="B9" s="2">
-        <v>46295.07291666666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>4967</v>
-      </c>
-      <c r="B10" s="2">
-        <v>46295.08333333334</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>4934</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46295.09375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>5145</v>
-      </c>
-      <c r="B12" s="2">
-        <v>46295.10416666666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>5103</v>
-      </c>
-      <c r="B13" s="2">
-        <v>46295.11458333334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>5062</v>
-      </c>
-      <c r="B14" s="2">
-        <v>46295.125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>5040</v>
-      </c>
-      <c r="B15" s="2">
-        <v>46295.13541666666</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>5127</v>
-      </c>
-      <c r="B16" s="2">
-        <v>46295.14583333334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>5242</v>
-      </c>
-      <c r="B17" s="2">
-        <v>46295.15625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>5201</v>
-      </c>
-      <c r="B18" s="2">
-        <v>46295.16666666666</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>5228</v>
-      </c>
-      <c r="B19" s="2">
-        <v>46295.17708333334</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>5350</v>
-      </c>
-      <c r="B20" s="2">
-        <v>46295.1875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>5433</v>
-      </c>
-      <c r="B21" s="2">
-        <v>46295.19791666666</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>5625</v>
-      </c>
-      <c r="B22" s="2">
-        <v>46295.20833333334</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>5618</v>
-      </c>
-      <c r="B23" s="2">
-        <v>46295.21875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>5745</v>
-      </c>
-      <c r="B24" s="2">
-        <v>46295.22916666666</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>5917</v>
-      </c>
-      <c r="B25" s="2">
-        <v>46295.23958333334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>6064</v>
-      </c>
-      <c r="B26" s="2">
-        <v>46295.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>6231</v>
-      </c>
-      <c r="B27" s="2">
-        <v>46295.26041666666</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>6312</v>
-      </c>
-      <c r="B28" s="2">
-        <v>46295.27083333334</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>6300</v>
-      </c>
-      <c r="B29" s="2">
-        <v>46295.28125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>6278</v>
-      </c>
-      <c r="B30" s="2">
-        <v>46295.29166666666</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>6324</v>
-      </c>
-      <c r="B31" s="2">
-        <v>46295.30208333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>6224</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46295.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>6112</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46295.32291666666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>5868</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46295.33333333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>5770</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46295.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>5641</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46295.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>5505</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46295.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>5199</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46295.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>5088</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46295.38541666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>5110</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46295.39583333334</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -26,6 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -78,11 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -388,6 +392,318 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>4523</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>4514</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46307.01041666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>4502</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46307.02083333334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4493</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46307.03125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4512</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46307.04166666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>4612</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46307.05208333334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>4655</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46307.0625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>4723</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46307.07291666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>4685</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46307.08333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>4792</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46307.09375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>4718</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46307.10416666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>4746</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46307.11458333334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>4702</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46307.125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>4759</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46307.13541666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>4769</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46307.14583333334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>4802</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46307.15625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>4829</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46307.16666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>4781</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46307.17708333334</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>4771</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46307.1875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>4828</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46307.19791666666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>5041</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46307.20833333334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>5233</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46307.21875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>5395</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46307.22916666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>5629</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46307.23958333334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>5899</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46307.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>6046</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46307.26041666666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>6227</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46307.27083333334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>6221</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46307.28125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>6427</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46307.29166666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>6536</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46307.30208333334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>6605</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46307.3125</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>6626</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46307.32291666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>6691</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46307.33333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>6729</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46307.34375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>6771</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46307.35416666666</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>6807</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46307.36458333334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>6634</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46307.375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>6627</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46307.38541666666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>6629</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46307.39583333334</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,314 +394,434 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>4523</v>
+        <v>5077</v>
       </c>
       <c r="B2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>4514</v>
+        <v>5009</v>
       </c>
       <c r="B3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>4502</v>
+        <v>5041</v>
       </c>
       <c r="B4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>4493</v>
+        <v>5017</v>
       </c>
       <c r="B5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4512</v>
+        <v>5098</v>
       </c>
       <c r="B6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4612</v>
+        <v>5036</v>
       </c>
       <c r="B7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>4655</v>
+        <v>5112</v>
       </c>
       <c r="B8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>4723</v>
+        <v>5094</v>
       </c>
       <c r="B9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>4685</v>
+        <v>5206</v>
       </c>
       <c r="B10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.09375</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>4792</v>
+        <v>5194</v>
       </c>
       <c r="B11" s="2">
-        <v>46307.09375</v>
+        <v>46308.10416666666</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>4718</v>
+        <v>5152</v>
       </c>
       <c r="B12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.11458333334</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>4746</v>
+        <v>5235</v>
       </c>
       <c r="B13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>4702</v>
+        <v>5234</v>
       </c>
       <c r="B14" s="2">
-        <v>46307.125</v>
+        <v>46308.13541666666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>4759</v>
+        <v>5184</v>
       </c>
       <c r="B15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.14583333334</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>4769</v>
+        <v>5106</v>
       </c>
       <c r="B16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.15625</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>4802</v>
+        <v>5028</v>
       </c>
       <c r="B17" s="2">
-        <v>46307.15625</v>
+        <v>46308.16666666666</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>4829</v>
+        <v>5104</v>
       </c>
       <c r="B18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.17708333334</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>4781</v>
+        <v>5121</v>
       </c>
       <c r="B19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.1875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>4771</v>
+        <v>5222</v>
       </c>
       <c r="B20" s="2">
-        <v>46307.1875</v>
+        <v>46308.19791666666</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>4828</v>
+        <v>5460</v>
       </c>
       <c r="B21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.20833333334</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5041</v>
+        <v>5655</v>
       </c>
       <c r="B22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.21875</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5233</v>
+        <v>5850</v>
       </c>
       <c r="B23" s="2">
-        <v>46307.21875</v>
+        <v>46308.22916666666</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5395</v>
+        <v>5950</v>
       </c>
       <c r="B24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.23958333334</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>5629</v>
+        <v>6298</v>
       </c>
       <c r="B25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.25</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>5899</v>
+        <v>6393</v>
       </c>
       <c r="B26" s="2">
-        <v>46307.25</v>
+        <v>46308.26041666666</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6046</v>
+        <v>6500</v>
       </c>
       <c r="B27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.27083333334</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6227</v>
+        <v>6550</v>
       </c>
       <c r="B28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.28125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6221</v>
+        <v>6676</v>
       </c>
       <c r="B29" s="2">
-        <v>46307.28125</v>
+        <v>46308.29166666666</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6427</v>
+        <v>6782</v>
       </c>
       <c r="B30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.30208333334</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6536</v>
+        <v>6833</v>
       </c>
       <c r="B31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.3125</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6605</v>
+        <v>6782</v>
       </c>
       <c r="B32" s="2">
-        <v>46307.3125</v>
+        <v>46308.32291666666</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6626</v>
+        <v>6763</v>
       </c>
       <c r="B33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.33333333334</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6691</v>
+        <v>6745</v>
       </c>
       <c r="B34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.34375</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>6729</v>
+        <v>6664</v>
       </c>
       <c r="B35" s="2">
-        <v>46307.34375</v>
+        <v>46308.35416666666</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>6771</v>
+        <v>6590</v>
       </c>
       <c r="B36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.36458333334</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>6807</v>
+        <v>6524</v>
       </c>
       <c r="B37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.375</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>6634</v>
+        <v>6505</v>
       </c>
       <c r="B38" s="2">
-        <v>46307.375</v>
+        <v>46308.38541666666</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>6627</v>
+        <v>6508</v>
       </c>
       <c r="B39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.39583333334</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>6629</v>
+        <v>6439</v>
       </c>
       <c r="B40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.40625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>6229</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46308.41666666666</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>6155</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46308.42708333334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>6094</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46308.4375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>6060</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46308.44791666666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>6023</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46308.45833333334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>6006</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46308.46875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>6156</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46308.47916666666</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>6218</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46308.48958333334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>6133</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46308.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>6190</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46308.51041666666</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>6220</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46308.52083333334</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>6211</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46308.53125</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>6213</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46308.54166666666</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>6174</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46308.55208333334</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>6152</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46308.5625</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,434 +394,474 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5077</v>
+        <v>5157</v>
       </c>
       <c r="B2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5009</v>
+        <v>5096</v>
       </c>
       <c r="B3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5041</v>
+        <v>5208</v>
       </c>
       <c r="B4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5017</v>
+        <v>5138</v>
       </c>
       <c r="B5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5098</v>
+        <v>4997</v>
       </c>
       <c r="B6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5036</v>
+        <v>5104</v>
       </c>
       <c r="B7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5112</v>
+        <v>5103</v>
       </c>
       <c r="B8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5094</v>
+        <v>5214</v>
       </c>
       <c r="B9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5206</v>
+        <v>5201</v>
       </c>
       <c r="B10" s="2">
-        <v>46308.09375</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5194</v>
+        <v>5207</v>
       </c>
       <c r="B11" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5152</v>
+        <v>5292</v>
       </c>
       <c r="B12" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5235</v>
+        <v>5325</v>
       </c>
       <c r="B13" s="2">
-        <v>46308.125</v>
+        <v>46309.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5234</v>
+        <v>5304</v>
       </c>
       <c r="B14" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5184</v>
+        <v>5320</v>
       </c>
       <c r="B15" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5106</v>
+        <v>5411</v>
       </c>
       <c r="B16" s="2">
-        <v>46308.15625</v>
+        <v>46309.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5028</v>
+        <v>5350</v>
       </c>
       <c r="B17" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5104</v>
+        <v>5236</v>
       </c>
       <c r="B18" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5121</v>
+        <v>5172</v>
       </c>
       <c r="B19" s="2">
-        <v>46308.1875</v>
+        <v>46309.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5222</v>
+        <v>5231</v>
       </c>
       <c r="B20" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5460</v>
+        <v>5317</v>
       </c>
       <c r="B21" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5655</v>
+        <v>5564</v>
       </c>
       <c r="B22" s="2">
-        <v>46308.21875</v>
+        <v>46309.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5850</v>
+        <v>5689</v>
       </c>
       <c r="B23" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5950</v>
+        <v>5869</v>
       </c>
       <c r="B24" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>6298</v>
+        <v>6042</v>
       </c>
       <c r="B25" s="2">
-        <v>46308.25</v>
+        <v>46309.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6393</v>
+        <v>6385</v>
       </c>
       <c r="B26" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6500</v>
+        <v>6484</v>
       </c>
       <c r="B27" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6550</v>
+        <v>6425</v>
       </c>
       <c r="B28" s="2">
-        <v>46308.28125</v>
+        <v>46309.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6676</v>
+        <v>6524</v>
       </c>
       <c r="B29" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6782</v>
+        <v>6717</v>
       </c>
       <c r="B30" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6833</v>
+        <v>6733</v>
       </c>
       <c r="B31" s="2">
-        <v>46308.3125</v>
+        <v>46309.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6782</v>
+        <v>6655</v>
       </c>
       <c r="B32" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6763</v>
+        <v>6717</v>
       </c>
       <c r="B33" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6745</v>
+        <v>6542</v>
       </c>
       <c r="B34" s="2">
-        <v>46308.34375</v>
+        <v>46309.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>6664</v>
+        <v>6446</v>
       </c>
       <c r="B35" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>6590</v>
+        <v>6358</v>
       </c>
       <c r="B36" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>6524</v>
+        <v>6395</v>
       </c>
       <c r="B37" s="2">
-        <v>46308.375</v>
+        <v>46309.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>6505</v>
+        <v>6032</v>
       </c>
       <c r="B38" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>6508</v>
+        <v>6007</v>
       </c>
       <c r="B39" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>6439</v>
+        <v>5700</v>
       </c>
       <c r="B40" s="2">
-        <v>46308.40625</v>
+        <v>46309.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>6229</v>
+        <v>5655</v>
       </c>
       <c r="B41" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>6155</v>
+        <v>5286</v>
       </c>
       <c r="B42" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>6094</v>
+        <v>5265</v>
       </c>
       <c r="B43" s="2">
-        <v>46308.4375</v>
+        <v>46309.42708333334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>6060</v>
+        <v>5236</v>
       </c>
       <c r="B44" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.4375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>6023</v>
+        <v>5137</v>
       </c>
       <c r="B45" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.44791666666</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>6006</v>
+        <v>4976</v>
       </c>
       <c r="B46" s="2">
-        <v>46308.46875</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>6156</v>
+        <v>4973</v>
       </c>
       <c r="B47" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.46875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>6218</v>
+        <v>4985</v>
       </c>
       <c r="B48" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.47916666666</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>6133</v>
+        <v>4873</v>
       </c>
       <c r="B49" s="2">
-        <v>46308.5</v>
+        <v>46309.48958333334</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>6190</v>
+        <v>4870</v>
       </c>
       <c r="B50" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.5</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>6220</v>
+        <v>4979</v>
       </c>
       <c r="B51" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.51041666666</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>6211</v>
+        <v>4950</v>
       </c>
       <c r="B52" s="2">
-        <v>46308.53125</v>
+        <v>46309.52083333334</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>6213</v>
+        <v>4816</v>
       </c>
       <c r="B53" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.53125</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>6174</v>
+        <v>4773</v>
       </c>
       <c r="B54" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.54166666666</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>6152</v>
+        <v>4766</v>
       </c>
       <c r="B55" s="2">
-        <v>46308.5625</v>
+        <v>46309.55208333334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>4728</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46309.5625</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>4723</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46309.57291666666</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>4768</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46309.58333333334</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>4699</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46309.59375</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>4588</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46309.60416666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,474 +394,410 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5157</v>
+        <v>5358</v>
       </c>
       <c r="B2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5096</v>
+        <v>5327</v>
       </c>
       <c r="B3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5208</v>
+        <v>5276</v>
       </c>
       <c r="B4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5138</v>
+        <v>5269</v>
       </c>
       <c r="B5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>4997</v>
+        <v>5268</v>
       </c>
       <c r="B6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5104</v>
+        <v>5249</v>
       </c>
       <c r="B7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5103</v>
+        <v>5253</v>
       </c>
       <c r="B8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5214</v>
+        <v>5263</v>
       </c>
       <c r="B9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5201</v>
+        <v>5302</v>
       </c>
       <c r="B10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5207</v>
+        <v>5297</v>
       </c>
       <c r="B11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5292</v>
+        <v>5330</v>
       </c>
       <c r="B12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5325</v>
+        <v>5296</v>
       </c>
       <c r="B13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5304</v>
+        <v>5362</v>
       </c>
       <c r="B14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5320</v>
+        <v>5376</v>
       </c>
       <c r="B15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5411</v>
+        <v>5308</v>
       </c>
       <c r="B16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5350</v>
+        <v>5304</v>
       </c>
       <c r="B17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5236</v>
+        <v>5324</v>
       </c>
       <c r="B18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5172</v>
+        <v>5366</v>
       </c>
       <c r="B19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5231</v>
+        <v>5428</v>
       </c>
       <c r="B20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5317</v>
+        <v>5558</v>
       </c>
       <c r="B21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5564</v>
+        <v>5751</v>
       </c>
       <c r="B22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5689</v>
+        <v>5851</v>
       </c>
       <c r="B23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5869</v>
+        <v>5963</v>
       </c>
       <c r="B24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>6042</v>
+        <v>6157</v>
       </c>
       <c r="B25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6385</v>
+        <v>6471</v>
       </c>
       <c r="B26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6484</v>
+        <v>6667</v>
       </c>
       <c r="B27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6425</v>
+        <v>6708</v>
       </c>
       <c r="B28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6524</v>
+        <v>6803</v>
       </c>
       <c r="B29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6717</v>
+        <v>6937</v>
       </c>
       <c r="B30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6733</v>
+        <v>6978</v>
       </c>
       <c r="B31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6655</v>
+        <v>6952</v>
       </c>
       <c r="B32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6717</v>
+        <v>6899</v>
       </c>
       <c r="B33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6542</v>
+        <v>6829</v>
       </c>
       <c r="B34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>6446</v>
+        <v>6745</v>
       </c>
       <c r="B35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>6358</v>
+        <v>6599</v>
       </c>
       <c r="B36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>6395</v>
+        <v>6515</v>
       </c>
       <c r="B37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>6032</v>
+        <v>6387</v>
       </c>
       <c r="B38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>6007</v>
+        <v>6222</v>
       </c>
       <c r="B39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>5700</v>
+        <v>6156</v>
       </c>
       <c r="B40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>5655</v>
+        <v>6097</v>
       </c>
       <c r="B41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>5286</v>
+        <v>5817</v>
       </c>
       <c r="B42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>5265</v>
+        <v>5758</v>
       </c>
       <c r="B43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>5236</v>
+        <v>5683</v>
       </c>
       <c r="B44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>5137</v>
+        <v>5580</v>
       </c>
       <c r="B45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>4976</v>
+        <v>5425</v>
       </c>
       <c r="B46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>4973</v>
+        <v>5452</v>
       </c>
       <c r="B47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>4985</v>
+        <v>5559</v>
       </c>
       <c r="B48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>4873</v>
+        <v>5616</v>
       </c>
       <c r="B49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>4870</v>
+        <v>5458</v>
       </c>
       <c r="B50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>4979</v>
+        <v>5363</v>
       </c>
       <c r="B51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>4950</v>
+        <v>5339</v>
       </c>
       <c r="B52" s="2">
-        <v>46309.52083333334</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>4816</v>
-      </c>
-      <c r="B53" s="2">
-        <v>46309.53125</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>4773</v>
-      </c>
-      <c r="B54" s="2">
-        <v>46309.54166666666</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>4766</v>
-      </c>
-      <c r="B55" s="2">
-        <v>46309.55208333334</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>4728</v>
-      </c>
-      <c r="B56" s="2">
-        <v>46309.5625</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>4723</v>
-      </c>
-      <c r="B57" s="2">
-        <v>46309.57291666666</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>4768</v>
-      </c>
-      <c r="B58" s="2">
-        <v>46309.58333333334</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>4699</v>
-      </c>
-      <c r="B59" s="2">
-        <v>46309.59375</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>4588</v>
-      </c>
-      <c r="B60" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.52083333334</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,410 +394,282 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5358</v>
+        <v>5265</v>
       </c>
       <c r="B2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5327</v>
+        <v>5213</v>
       </c>
       <c r="B3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5276</v>
+        <v>5250</v>
       </c>
       <c r="B4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5269</v>
+        <v>5207</v>
       </c>
       <c r="B5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5268</v>
+        <v>5226</v>
       </c>
       <c r="B6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5249</v>
+        <v>5286</v>
       </c>
       <c r="B7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5253</v>
+        <v>5181</v>
       </c>
       <c r="B8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5263</v>
+        <v>5176</v>
       </c>
       <c r="B9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5302</v>
+        <v>5168</v>
       </c>
       <c r="B10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5297</v>
+        <v>5167</v>
       </c>
       <c r="B11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5330</v>
+        <v>5208</v>
       </c>
       <c r="B12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5296</v>
+        <v>5144</v>
       </c>
       <c r="B13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5362</v>
+        <v>5186</v>
       </c>
       <c r="B14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5376</v>
+        <v>5200</v>
       </c>
       <c r="B15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5308</v>
+        <v>5211</v>
       </c>
       <c r="B16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5304</v>
+        <v>5232</v>
       </c>
       <c r="B17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5324</v>
+        <v>5322</v>
       </c>
       <c r="B18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5366</v>
+        <v>5309</v>
       </c>
       <c r="B19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5428</v>
+        <v>5338</v>
       </c>
       <c r="B20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5558</v>
+        <v>5353</v>
       </c>
       <c r="B21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5751</v>
+        <v>5695</v>
       </c>
       <c r="B22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5851</v>
+        <v>5740</v>
       </c>
       <c r="B23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5963</v>
+        <v>5960</v>
       </c>
       <c r="B24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>6157</v>
+        <v>6103</v>
       </c>
       <c r="B25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6471</v>
+        <v>6433</v>
       </c>
       <c r="B26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6667</v>
+        <v>6620</v>
       </c>
       <c r="B27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6708</v>
+        <v>6692</v>
       </c>
       <c r="B28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6803</v>
+        <v>6813</v>
       </c>
       <c r="B29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6937</v>
+        <v>6867</v>
       </c>
       <c r="B30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6978</v>
+        <v>6940</v>
       </c>
       <c r="B31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>6952</v>
+        <v>6931</v>
       </c>
       <c r="B32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>6899</v>
+        <v>6966</v>
       </c>
       <c r="B33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>6829</v>
+        <v>6840</v>
       </c>
       <c r="B34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>6745</v>
+        <v>6783</v>
       </c>
       <c r="B35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>6599</v>
+        <v>6613</v>
       </c>
       <c r="B36" s="2">
-        <v>46311.35416666666</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>6515</v>
-      </c>
-      <c r="B37" s="2">
-        <v>46311.36458333334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>6387</v>
-      </c>
-      <c r="B38" s="2">
-        <v>46311.375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>6222</v>
-      </c>
-      <c r="B39" s="2">
-        <v>46311.38541666666</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>6156</v>
-      </c>
-      <c r="B40" s="2">
-        <v>46311.39583333334</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>6097</v>
-      </c>
-      <c r="B41" s="2">
-        <v>46311.40625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>5817</v>
-      </c>
-      <c r="B42" s="2">
-        <v>46311.41666666666</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>5758</v>
-      </c>
-      <c r="B43" s="2">
-        <v>46311.42708333334</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>5683</v>
-      </c>
-      <c r="B44" s="2">
-        <v>46311.4375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>5580</v>
-      </c>
-      <c r="B45" s="2">
-        <v>46311.44791666666</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>5425</v>
-      </c>
-      <c r="B46" s="2">
-        <v>46311.45833333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>5452</v>
-      </c>
-      <c r="B47" s="2">
-        <v>46311.46875</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>5559</v>
-      </c>
-      <c r="B48" s="2">
-        <v>46311.47916666666</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>5616</v>
-      </c>
-      <c r="B49" s="2">
-        <v>46311.48958333334</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>5458</v>
-      </c>
-      <c r="B50" s="2">
-        <v>46311.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>5363</v>
-      </c>
-      <c r="B51" s="2">
-        <v>46311.51041666666</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>5339</v>
-      </c>
-      <c r="B52" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.35416666666</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Actual.xlsx
+++ b/data_fetching/Entsoe/Consumption_Actual.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,282 +394,242 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>5265</v>
+        <v>4972</v>
       </c>
       <c r="B2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>5213</v>
+        <v>4941</v>
       </c>
       <c r="B3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>5250</v>
+        <v>4973</v>
       </c>
       <c r="B4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5207</v>
+        <v>4965</v>
       </c>
       <c r="B5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>5226</v>
+        <v>4839</v>
       </c>
       <c r="B6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>5286</v>
+        <v>4856</v>
       </c>
       <c r="B7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5181</v>
+        <v>4880</v>
       </c>
       <c r="B8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5176</v>
+        <v>4790</v>
       </c>
       <c r="B9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>5168</v>
+        <v>4778</v>
       </c>
       <c r="B10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>5167</v>
+        <v>4687</v>
       </c>
       <c r="B11" s="2">
-        <v>46316.09375</v>
+        <v>46320.13541666666</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>5208</v>
+        <v>4721</v>
       </c>
       <c r="B12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.14583333334</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>5144</v>
+        <v>4698</v>
       </c>
       <c r="B13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.15625</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>5186</v>
+        <v>4749</v>
       </c>
       <c r="B14" s="2">
-        <v>46316.125</v>
+        <v>46320.16666666666</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>5200</v>
+        <v>4772</v>
       </c>
       <c r="B15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.17708333334</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>5211</v>
+        <v>4807</v>
       </c>
       <c r="B16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.1875</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>5232</v>
+        <v>4811</v>
       </c>
       <c r="B17" s="2">
-        <v>46316.15625</v>
+        <v>46320.19791666666</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>5322</v>
+        <v>4911</v>
       </c>
       <c r="B18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>5309</v>
+        <v>4935</v>
       </c>
       <c r="B19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.21875</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>5338</v>
+        <v>4967</v>
       </c>
       <c r="B20" s="2">
-        <v>46316.1875</v>
+        <v>46320.22916666666</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>5353</v>
+        <v>4922</v>
       </c>
       <c r="B21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.23958333334</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>5695</v>
+        <v>4987</v>
       </c>
       <c r="B22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.25</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>5740</v>
+        <v>5018</v>
       </c>
       <c r="B23" s="2">
-        <v>46316.21875</v>
+        <v>46320.26041666666</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>5960</v>
+        <v>5034</v>
       </c>
       <c r="B24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.27083333334</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>6103</v>
+        <v>4976</v>
       </c>
       <c r="B25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.28125</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>6433</v>
+        <v>4954</v>
       </c>
       <c r="B26" s="2">
-        <v>46316.25</v>
+        <v>46320.29166666666</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>6620</v>
+        <v>4979</v>
       </c>
       <c r="B27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.30208333334</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>6692</v>
+        <v>4909</v>
       </c>
       <c r="B28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.3125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>6813</v>
+        <v>4809</v>
       </c>
       <c r="B29" s="2">
-        <v>46316.28125</v>
+        <v>46320.32291666666</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>6867</v>
+        <v>4702</v>
       </c>
       <c r="B30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.33333333334</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>6940</v>
+        <v>4617</v>
       </c>
       <c r="B31" s="2">
-        <v>46316.30208333334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>6931</v>
-      </c>
-      <c r="B32" s="2">
-        <v>46316.3125</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>6966</v>
-      </c>
-      <c r="B33" s="2">
-        <v>46316.32291666666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>6840</v>
-      </c>
-      <c r="B34" s="2">
-        <v>46316.33333333334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>6783</v>
-      </c>
-      <c r="B35" s="2">
-        <v>46316.34375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>6613</v>
-      </c>
-      <c r="B36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.34375</v>
       </c>
     </row>
   </sheetData>
